--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.1-8B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.1-8B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>180</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="G2">
-        <v>406</v>
+        <v>172</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>136</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="G3">
-        <v>415</v>
+        <v>180</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.1-8B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.1-8B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2">
-        <v>180</v>
+        <v>146</v>
       </c>
       <c r="E2">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="G2">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D3">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="E3">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="G3">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="H3">
         <v>426</v>
